--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Madhuravoyal_to_Madiwala/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Madhuravoyal_to_Madiwala/Average/Master_Results.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Phase_Difference_Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Descriptive_Statistics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Route_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Plot_Audit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF3"/>
+  <dimension ref="A1:BF7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,11 +727,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,174 +750,174 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_038_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>184.8808833333333</v>
+        <v>395</v>
       </c>
       <c r="H2" t="n">
-        <v>189.0966166666667</v>
+        <v>374.9615166666666</v>
       </c>
       <c r="I2" t="n">
-        <v>159.8172074707595</v>
+        <v>326.3547725745892</v>
       </c>
       <c r="J2" t="n">
-        <v>159.58380997156</v>
+        <v>325.9460971942599</v>
       </c>
       <c r="K2" t="n">
-        <v>58.20216621959079</v>
+        <v>61.31623721877904</v>
       </c>
       <c r="L2" t="n">
-        <v>55.92805804691302</v>
+        <v>59.54001701508474</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.215733333333418</v>
+        <v>20.03848333333337</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2333974991995262</v>
+        <v>0.4086753803293277</v>
       </c>
       <c r="O2" t="n">
-        <v>2.274108172677764</v>
+        <v>1.776220203694294</v>
       </c>
       <c r="P2" t="n">
-        <v>2.166666666666671</v>
+        <v>-21.38333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="W2" t="n">
-        <v>3.95</v>
+        <v>8.366666666666667</v>
       </c>
       <c r="X2" t="n">
-        <v>14.68333333333333</v>
+        <v>42.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>-10.73333333333333</v>
+        <v>-34.28333333333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1908765853606127</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1830132758657204</v>
+        <v>0.54761889554039</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1180389999231207</v>
+        <v>-0.3567423101797773</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.35</v>
+        <v>17.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.45</v>
+        <v>4.45</v>
       </c>
       <c r="AE2" t="n">
         <v>12.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1028343892545171</v>
+        <v>0.1087001286100384</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.04005612640255141</v>
+        <v>0.050473616639225</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.06277826285196569</v>
+        <v>0.0582265119708134</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.68333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="AK2" t="n">
-        <v>-7.43333333333333</v>
+        <v>-7.266666666666669</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2821742444234817</v>
+        <v>0.398684318669226</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6170753744976548</v>
+        <v>0.9451362793530877</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.3349011300741731</v>
+        <v>-0.5464519606838618</v>
       </c>
       <c r="AO2" t="n">
-        <v>40.2</v>
+        <v>75.68333333333334</v>
       </c>
       <c r="AP2" t="n">
-        <v>26.06666666666667</v>
+        <v>57.41151666666666</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.13333333333333</v>
+        <v>18.27181666666668</v>
       </c>
       <c r="AR2" t="n">
-        <v>34.54349490383015</v>
+        <v>67.35824904037362</v>
       </c>
       <c r="AS2" t="n">
-        <v>22.28483087263108</v>
+        <v>50.57101621965544</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.25866403119907</v>
+        <v>16.78723282071818</v>
       </c>
       <c r="AU2" t="n">
-        <v>29.63088333333333</v>
+        <v>57.18333333333333</v>
       </c>
       <c r="AV2" t="n">
-        <v>22.58333333333333</v>
+        <v>49.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.047550000000001</v>
+        <v>7.583333333333329</v>
       </c>
       <c r="AX2" t="n">
-        <v>26.48638220201241</v>
+        <v>52.26279143298722</v>
       </c>
       <c r="AY2" t="n">
-        <v>19.99284056290314</v>
+        <v>45.61259697139702</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.493541639109271</v>
+        <v>6.650194461590203</v>
       </c>
       <c r="BA2" t="n">
-        <v>91.5</v>
+        <v>181.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>111.62995</v>
+        <v>208.8333333333333</v>
       </c>
       <c r="BC2" t="n">
-        <v>-20.12994999999999</v>
+        <v>-27.53333333333327</v>
       </c>
       <c r="BD2" t="n">
-        <v>98.33734745529641</v>
+        <v>205.8931083138968</v>
       </c>
       <c r="BE2" t="n">
-        <v>116.4659937592599</v>
+        <v>228.2192552116748</v>
       </c>
       <c r="BF2" t="n">
-        <v>-18.12864630396349</v>
+        <v>-22.32614689777802</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,164 +936,908 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_039_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>66.01939999999999</v>
+        <v>392.3709333333334</v>
       </c>
       <c r="H3" t="n">
-        <v>94.14933333333333</v>
+        <v>411.8826166666667</v>
       </c>
       <c r="I3" t="n">
-        <v>49.09342708546251</v>
+        <v>325.4159138009351</v>
       </c>
       <c r="J3" t="n">
-        <v>49.01363547616007</v>
+        <v>325.0535176750399</v>
       </c>
       <c r="K3" t="n">
-        <v>47.58550177729312</v>
+        <v>61.64781186469645</v>
       </c>
       <c r="L3" t="n">
-        <v>37.18511343393678</v>
+        <v>56.977909507314</v>
       </c>
       <c r="M3" t="n">
-        <v>-28.12993333333334</v>
+        <v>-19.51168333333328</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07979160930243978</v>
+        <v>0.3623961258951454</v>
       </c>
       <c r="O3" t="n">
-        <v>10.40038834335634</v>
+        <v>4.669902357382448</v>
       </c>
       <c r="P3" t="n">
-        <v>-11.5</v>
+        <v>-44.93333333333334</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+      <c r="W3" t="n">
+        <v>8.366666666666667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>62.76666666666667</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-54.40000000000001</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.1908765853606127</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.9031778355480963</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.7123012501874836</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>7.883333333333334</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>9.466666666666669</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1087001286100384</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.1049872832033934</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.003712845406645002</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.3780850080592794</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.6373216143401321</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.2592366062808527</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>74.78333333333333</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>67.35806666666666</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.425266666666673</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>67.00799281022444</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>52.91266607635799</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>14.09532673386644</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>56.4376</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>47.91666666666666</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.520933333333346</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>52.06628269419153</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>38.05595749464888</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.01032519954265</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>180.4833333333333</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>222.97455</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-42.4912166666667</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>205.5216138197976</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>232.4394073709414</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-26.9177935511438</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_02-10-2026\PAIR_040_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>395</v>
+      </c>
+      <c r="H4" t="n">
+        <v>319.5048166666667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>326.4235517768342</v>
+      </c>
+      <c r="J4" t="n">
+        <v>325.9521091087573</v>
+      </c>
+      <c r="K4" t="n">
+        <v>61.32917712617816</v>
+      </c>
+      <c r="L4" t="n">
+        <v>62.63705094403212</v>
+      </c>
+      <c r="M4" t="n">
+        <v>75.49518333333327</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4714426680768611</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1.30787381785396</v>
+      </c>
+      <c r="P4" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-10.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.06497427594259966</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.3781894421708778</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.3132151662282782</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="S4" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="AG3" t="n">
-        <v>0.01632338704389566</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.01632338704389566</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-0.6499999999999999</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.07825898700519315</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.1903594564923157</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-0.1121004694871225</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>21.19846666666666</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24.53266666666667</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-3.33420000000001</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>17.20758212650452</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>16.02491169354092</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.182670432963601</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>15.75426666666667</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17.41666666666667</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-1.662400000000002</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12.63780002856964</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11.032089516834</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.605710511735639</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>23.86666666666667</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-10.98333333333333</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.10481166744055</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>21.37176198007807</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-2.266950312637519</v>
+      <c r="V4" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+      <c r="W4" t="n">
+        <v>8.366666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.016666666666667</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1908765853606127</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.002166493188354733</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.188710092172258</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1087001286100384</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.04085835435001741</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.067841774260021</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.866666666666667</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.398684318669226</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.3612962495734293</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.03738806909579667</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>75.68333333333334</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>49.16666666666666</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>26.51666666666668</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>67.35824904037362</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>42.50561741506265</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>24.85263162531097</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>57.18333333333333</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21.84999999999999</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>52.27381680184341</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>30.72869553457691</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>21.5451212672665</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>225.8048166666667</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-44.5048166666667</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>205.9508621472857</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>252.313475062006</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-46.3626129147203</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_02-10-2026\PAIR_041_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="H5" t="n">
+        <v>372.5504</v>
+      </c>
+      <c r="I5" t="n">
+        <v>325.4492993959398</v>
+      </c>
+      <c r="J5" t="n">
+        <v>325.1974783974341</v>
+      </c>
+      <c r="K5" t="n">
+        <v>67.12149214202077</v>
+      </c>
+      <c r="L5" t="n">
+        <v>59.84310713127186</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-18.70255000000003</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2518209985057069</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7.278385010748913</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-28.66666666666667</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="X5" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-35.96666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.54761889554039</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.4206047995376859</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.050473616639225</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.01892500794871542</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>12.01666666666667</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.9451362793530877</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.7776330884380754</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>56.91666666666666</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.38333333333334</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>59.99350553918008</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>50.23554888844169</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.757956650738386</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>49.01706666666666</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.849600000000009</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>45.36220285483913</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8.460916813254315</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-34.95214999999999</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>211.2543855609569</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>228.0564978626206</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-16.8021123016637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>47</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-09-2026_to_02-10-2026\PAIR_047_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="H6" t="n">
+        <v>412.4881333333333</v>
+      </c>
+      <c r="I6" t="n">
+        <v>325.3816512944114</v>
+      </c>
+      <c r="J6" t="n">
+        <v>325.1731293793417</v>
+      </c>
+      <c r="K6" t="n">
+        <v>67.10753118315435</v>
+      </c>
+      <c r="L6" t="n">
+        <v>57.06712981492286</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-58.64028333333329</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2085219150697526</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10.04040136823149</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-53.23333333333333</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="W6" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="X6" t="n">
+        <v>62.76666666666667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-56.08333333333334</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.9031778355480963</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.7761637395453922</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.108236844142404</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.07668823545189443</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-1.283333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.6481534841388865</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.4806502932238742</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>67.36666666666666</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-3.066666666666663</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>59.94580589720089</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>52.96068060572409</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.985125291476798</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>48.23333333333333</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.63333333333334</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>38.3638733890867</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15.45924627900675</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>221.9214666666667</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-49.37361666666669</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>211.2344371014078</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>232.1890072207015</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-20.95457011929372</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>53</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\02-10-2026\PAIR_053_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="H7" t="n">
+        <v>317.9467666666667</v>
+      </c>
+      <c r="I7" t="n">
+        <v>325.4090582064992</v>
+      </c>
+      <c r="J7" t="n">
+        <v>325.0956316318464</v>
+      </c>
+      <c r="K7" t="n">
+        <v>67.11318731782285</v>
+      </c>
+      <c r="L7" t="n">
+        <v>62.7857905819767</v>
+      </c>
+      <c r="M7" t="n">
+        <v>35.9010833333333</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3134265746527944</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.32739673584615</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.11666666666667</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.016666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.002166493188354733</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1248476028143494</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.04085835435001741</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.009309745659507832</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.133333333333334</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.3612962495734293</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.193793058658417</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>48.91343333333334</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>15.38656666666666</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>59.94209820275543</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>42.40876109368212</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>17.53333710907331</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>16.53333333333332</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>30.72869553457691</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>23.09442413351654</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-51.95214999999999</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>211.265551707941</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>251.5538539064756</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-40.28830219853461</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,7 +1899,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1165,28 +1908,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1195,28 +1938,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.95</v>
+        <v>8.366666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>14.68333333333333</v>
+        <v>42.65</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.73333333333333</v>
+        <v>-34.28333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1908765853606127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1830132758657204</v>
+        <v>0.54761889554039</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1180389999231207</v>
+        <v>-0.3567423101797773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1225,28 +1968,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.35</v>
+        <v>17.35</v>
       </c>
       <c r="D4" t="n">
-        <v>3.45</v>
+        <v>4.45</v>
       </c>
       <c r="E4" t="n">
         <v>12.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1028343892545171</v>
+        <v>0.1087001286100384</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04005612640255141</v>
+        <v>0.050473616639225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06277826285196569</v>
+        <v>0.0582265119708134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1255,28 +1998,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="D5" t="n">
-        <v>10.68333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.43333333333333</v>
+        <v>-7.266666666666669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2821742444234817</v>
+        <v>0.398684318669226</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6170753744976548</v>
+        <v>0.9451362793530877</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3349011300741731</v>
+        <v>-0.5464519606838618</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1285,28 +2028,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.2</v>
+        <v>75.68333333333334</v>
       </c>
       <c r="D6" t="n">
-        <v>26.06666666666667</v>
+        <v>57.41151666666666</v>
       </c>
       <c r="E6" t="n">
-        <v>14.13333333333333</v>
+        <v>18.27181666666668</v>
       </c>
       <c r="F6" t="n">
-        <v>34.54349490383015</v>
+        <v>67.35824904037362</v>
       </c>
       <c r="G6" t="n">
-        <v>22.28483087263108</v>
+        <v>50.57101621965544</v>
       </c>
       <c r="H6" t="n">
-        <v>12.25866403119907</v>
+        <v>16.78723282071818</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1315,28 +2058,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.63088333333333</v>
+        <v>57.18333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>22.58333333333333</v>
+        <v>49.6</v>
       </c>
       <c r="E7" t="n">
-        <v>7.047550000000001</v>
+        <v>7.583333333333329</v>
       </c>
       <c r="F7" t="n">
-        <v>26.48638220201241</v>
+        <v>52.26279143298722</v>
       </c>
       <c r="G7" t="n">
-        <v>19.99284056290314</v>
+        <v>45.61259697139702</v>
       </c>
       <c r="H7" t="n">
-        <v>6.493541639109271</v>
+        <v>6.650194461590203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1345,28 +2088,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.5</v>
+        <v>181.3</v>
       </c>
       <c r="D8" t="n">
-        <v>111.62995</v>
+        <v>208.8333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.12994999999999</v>
+        <v>-27.53333333333327</v>
       </c>
       <c r="F8" t="n">
-        <v>98.33734745529641</v>
+        <v>205.8931083138968</v>
       </c>
       <c r="G8" t="n">
-        <v>116.4659937592599</v>
+        <v>228.2192552116748</v>
       </c>
       <c r="H8" t="n">
-        <v>-18.12864630396349</v>
+        <v>-22.32614689777802</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1375,28 +2118,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1405,28 +2148,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.95</v>
+        <v>8.366666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>14.7</v>
+        <v>62.76666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.75</v>
+        <v>-54.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1908765853606127</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3781894421708778</v>
+        <v>0.9031778355480963</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3132151662282782</v>
+        <v>-0.7123012501874836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1435,28 +2178,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
+        <v>17.35</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>7.883333333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.75</v>
+        <v>9.466666666666669</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.1087001286100384</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01632338704389566</v>
+        <v>0.1049872832033934</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01632338704389566</v>
+        <v>0.003712845406645002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1465,28 +2208,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65</v>
+        <v>2.983333333333333</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6499999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07825898700519315</v>
+        <v>0.3780850080592794</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1903594564923157</v>
+        <v>0.6373216143401321</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1121004694871225</v>
+        <v>-0.2592366062808527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1495,28 +2238,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.19846666666666</v>
+        <v>74.78333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>24.53266666666667</v>
+        <v>67.35806666666666</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.33420000000001</v>
+        <v>7.425266666666673</v>
       </c>
       <c r="F13" t="n">
-        <v>17.20758212650452</v>
+        <v>67.00799281022444</v>
       </c>
       <c r="G13" t="n">
-        <v>16.02491169354092</v>
+        <v>52.91266607635799</v>
       </c>
       <c r="H13" t="n">
-        <v>1.182670432963601</v>
+        <v>14.09532673386644</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1525,28 +2268,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.75426666666667</v>
+        <v>56.4376</v>
       </c>
       <c r="D14" t="n">
-        <v>17.41666666666667</v>
+        <v>47.91666666666666</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.662400000000002</v>
+        <v>8.520933333333346</v>
       </c>
       <c r="F14" t="n">
-        <v>12.63780002856964</v>
+        <v>52.06628269419153</v>
       </c>
       <c r="G14" t="n">
-        <v>11.032089516834</v>
+        <v>38.05595749464888</v>
       </c>
       <c r="H14" t="n">
-        <v>1.605710511735639</v>
+        <v>14.01032519954265</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_039</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1555,22 +2298,862 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.86666666666667</v>
+        <v>180.4833333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>34.85</v>
+        <v>222.97455</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.98333333333333</v>
+        <v>-42.4912166666667</v>
       </c>
       <c r="F15" t="n">
-        <v>19.10481166744055</v>
+        <v>205.5216138197976</v>
       </c>
       <c r="G15" t="n">
-        <v>21.37176198007807</v>
+        <v>232.4394073709414</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.266950312637519</v>
+        <v>-26.9177935511438</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8.366666666666667</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.016666666666667</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1908765853606127</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002166493188354733</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.188710092172258</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1087001286100384</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.04085835435001741</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.067841774260021</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.866666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.398684318669226</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3612962495734293</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.03738806909579667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>75.68333333333334</v>
+      </c>
+      <c r="D20" t="n">
+        <v>49.16666666666666</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.51666666666668</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67.35824904037362</v>
+      </c>
+      <c r="G20" t="n">
+        <v>42.50561741506265</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.85263162531097</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>57.18333333333333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="E21" t="n">
+        <v>21.84999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>52.27381680184341</v>
+      </c>
+      <c r="G21" t="n">
+        <v>30.72869553457691</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21.5451212672665</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>225.8048166666667</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-44.5048166666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>205.9508621472857</v>
+      </c>
+      <c r="G22" t="n">
+        <v>252.313475062006</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-46.3626129147203</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="D24" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-35.96666666666667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.54761889554039</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.4206047995376859</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.050473616639225</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01892500794871542</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12.01666666666667</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9451362793530877</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.7776330884380754</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>56.91666666666666</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.38333333333334</v>
+      </c>
+      <c r="F27" t="n">
+        <v>59.99350553918008</v>
+      </c>
+      <c r="G27" t="n">
+        <v>50.23554888844169</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9.757956650738386</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="D28" t="n">
+        <v>49.01706666666666</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.849600000000009</v>
+      </c>
+      <c r="F28" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="G28" t="n">
+        <v>45.36220285483913</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.460916813254315</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="D29" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-34.95214999999999</v>
+      </c>
+      <c r="F29" t="n">
+        <v>211.2543855609569</v>
+      </c>
+      <c r="G29" t="n">
+        <v>228.0564978626206</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-16.8021123016637</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="D31" t="n">
+        <v>62.76666666666667</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-56.08333333333334</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9031778355480963</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.7761637395453922</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.108236844142404</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.07668823545189443</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.283333333333333</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6481534841388865</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.4806502932238742</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>67.36666666666666</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-3.066666666666663</v>
+      </c>
+      <c r="F34" t="n">
+        <v>59.94580589720089</v>
+      </c>
+      <c r="G34" t="n">
+        <v>52.96068060572409</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6.985125291476798</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="D35" t="n">
+        <v>48.23333333333333</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.63333333333334</v>
+      </c>
+      <c r="F35" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="G35" t="n">
+        <v>38.3638733890867</v>
+      </c>
+      <c r="H35" t="n">
+        <v>15.45924627900675</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="D36" t="n">
+        <v>221.9214666666667</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-49.37361666666669</v>
+      </c>
+      <c r="F36" t="n">
+        <v>211.2344371014078</v>
+      </c>
+      <c r="G36" t="n">
+        <v>232.1890072207015</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-20.95457011929372</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.016666666666667</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.002166493188354733</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1248476028143494</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.04085835435001741</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.009309745659507832</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.133333333333334</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3612962495734293</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.193793058658417</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>48.91343333333334</v>
+      </c>
+      <c r="E41" t="n">
+        <v>15.38656666666666</v>
+      </c>
+      <c r="F41" t="n">
+        <v>59.94209820275543</v>
+      </c>
+      <c r="G41" t="n">
+        <v>42.40876109368212</v>
+      </c>
+      <c r="H41" t="n">
+        <v>17.53333710907331</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="D42" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.53333333333332</v>
+      </c>
+      <c r="F42" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30.72869553457691</v>
+      </c>
+      <c r="H42" t="n">
+        <v>23.09442413351654</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="D43" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-51.95214999999999</v>
+      </c>
+      <c r="F43" t="n">
+        <v>211.265551707941</v>
+      </c>
+      <c r="G43" t="n">
+        <v>251.5538539064756</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-40.28830219853461</v>
       </c>
     </row>
   </sheetData>
@@ -1631,19 +3214,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.09729274339634443</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1656,22 +3239,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.95</v>
+        <v>7.525000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>14.69166666666666</v>
+        <v>36.14444444444445</v>
       </c>
       <c r="D3" t="n">
-        <v>-10.74166666666667</v>
+        <v>-28.61944444444444</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.74166666666667</v>
+        <v>-35.125</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1589453406816584</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2806013590182991</v>
+        <v>0.484321074758947</v>
       </c>
     </row>
     <row r="4">
@@ -1681,22 +3264,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.300000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="C4" t="n">
-        <v>2.225</v>
+        <v>5.713888888888889</v>
       </c>
       <c r="D4" t="n">
-        <v>6.075000000000001</v>
+        <v>8.836111111111112</v>
       </c>
       <c r="E4" t="n">
-        <v>6.075000000000001</v>
+        <v>8.458333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05141719462725855</v>
+        <v>0.07012436865027399</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02818975672322354</v>
+        <v>0.06598134488738037</v>
       </c>
     </row>
     <row r="5">
@@ -1706,22 +3289,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.125</v>
+        <v>3.355555555555556</v>
       </c>
       <c r="C5" t="n">
-        <v>6.166666666666665</v>
+        <v>5.680555555555556</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.041666666666665</v>
+        <v>-2.325000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.041666666666665</v>
+        <v>-0.5749999999999994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1802166157143374</v>
+        <v>0.2796605363571281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4037174154949852</v>
+        <v>0.6497233593886754</v>
       </c>
     </row>
     <row r="6">
@@ -1731,22 +3314,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.69923333333333</v>
+        <v>69.84166666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>25.29966666666667</v>
+        <v>57.85550277777777</v>
       </c>
       <c r="D6" t="n">
-        <v>5.399566666666662</v>
+        <v>11.9861638888889</v>
       </c>
       <c r="E6" t="n">
-        <v>5.399566666666662</v>
+        <v>11.40591666666667</v>
       </c>
       <c r="F6" t="n">
-        <v>25.87553851516734</v>
+        <v>63.60098342168468</v>
       </c>
       <c r="G6" t="n">
-        <v>19.154871283086</v>
+        <v>48.59904838315399</v>
       </c>
     </row>
     <row r="7">
@@ -1756,22 +3339,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.692575</v>
+        <v>54.40071111111111</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>44.23895555555556</v>
       </c>
       <c r="D7" t="n">
-        <v>2.692575</v>
+        <v>10.16175555555556</v>
       </c>
       <c r="E7" t="n">
-        <v>2.692575</v>
+        <v>8.052133333333337</v>
       </c>
       <c r="F7" t="n">
-        <v>19.56209111529103</v>
+        <v>53.01204165555041</v>
       </c>
       <c r="G7" t="n">
-        <v>15.51246503986857</v>
+        <v>38.14200362985426</v>
       </c>
     </row>
     <row r="8">
@@ -1781,22 +3364,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57.68333333333334</v>
+        <v>176.7878138888889</v>
       </c>
       <c r="C8" t="n">
-        <v>73.239975</v>
+        <v>218.5890277777778</v>
       </c>
       <c r="D8" t="n">
-        <v>-15.55664166666666</v>
+        <v>-41.80121388888889</v>
       </c>
       <c r="E8" t="n">
-        <v>-15.55664166666666</v>
+        <v>-43.4980166666667</v>
       </c>
       <c r="F8" t="n">
-        <v>58.72107956136848</v>
+        <v>208.5199931085476</v>
       </c>
       <c r="G8" t="n">
-        <v>68.91887786966899</v>
+        <v>237.4619161057367</v>
       </c>
     </row>
   </sheetData>
@@ -1867,28 +3450,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>33.5</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7071067811865476</v>
+        <v>5.830951894845301</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>33.25</v>
+        <v>39.25</v>
       </c>
       <c r="G2" t="n">
-        <v>33.5</v>
+        <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>33.75</v>
+        <v>45.5</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -1898,28 +3481,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>125.4501416666666</v>
+        <v>373.9857472222222</v>
       </c>
       <c r="D3" t="n">
-        <v>84.04776088689177</v>
+        <v>22.08083975556743</v>
       </c>
       <c r="E3" t="n">
-        <v>66.01939999999999</v>
+        <v>353.84785</v>
       </c>
       <c r="F3" t="n">
-        <v>95.73477083333331</v>
+        <v>353.84785</v>
       </c>
       <c r="G3" t="n">
-        <v>125.4501416666666</v>
+        <v>373.1093916666667</v>
       </c>
       <c r="H3" t="n">
-        <v>155.1655125</v>
+        <v>394.3427333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>184.8808833333333</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -1929,28 +3512,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>141.622975</v>
+        <v>368.222375</v>
       </c>
       <c r="D4" t="n">
-        <v>67.13786790024049</v>
+        <v>42.02584723064913</v>
       </c>
       <c r="E4" t="n">
-        <v>94.14933333333333</v>
+        <v>317.9467666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>117.8861541666667</v>
+        <v>332.7662125000001</v>
       </c>
       <c r="G4" t="n">
-        <v>141.622975</v>
+        <v>373.7559583333333</v>
       </c>
       <c r="H4" t="n">
-        <v>165.3597958333334</v>
+        <v>402.6523416666667</v>
       </c>
       <c r="I4" t="n">
-        <v>189.0966166666667</v>
+        <v>412.4881333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1960,28 +3543,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>104.455317278111</v>
+        <v>325.7390411748681</v>
       </c>
       <c r="D5" t="n">
-        <v>78.29353594905355</v>
+        <v>0.5045112100071262</v>
       </c>
       <c r="E5" t="n">
-        <v>49.09342708546251</v>
+        <v>325.3816512944114</v>
       </c>
       <c r="F5" t="n">
-        <v>76.77437218178676</v>
+        <v>325.4107721051082</v>
       </c>
       <c r="G5" t="n">
-        <v>104.455317278111</v>
+        <v>325.4326065984375</v>
       </c>
       <c r="H5" t="n">
-        <v>132.1362623744353</v>
+        <v>326.1284042799269</v>
       </c>
       <c r="I5" t="n">
-        <v>159.8172074707595</v>
+        <v>326.4235517768342</v>
       </c>
     </row>
     <row r="6">
@@ -1991,28 +3574,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>104.29872272386</v>
+        <v>325.4029938977799</v>
       </c>
       <c r="D6" t="n">
-        <v>78.18492018267713</v>
+        <v>0.4261849870827946</v>
       </c>
       <c r="E6" t="n">
-        <v>49.01363547616007</v>
+        <v>325.0535176750399</v>
       </c>
       <c r="F6" t="n">
-        <v>76.65617910001005</v>
+        <v>325.1150060687202</v>
       </c>
       <c r="G6" t="n">
-        <v>104.29872272386</v>
+        <v>325.1853038883879</v>
       </c>
       <c r="H6" t="n">
-        <v>131.94126634771</v>
+        <v>325.7589424950535</v>
       </c>
       <c r="I6" t="n">
-        <v>159.58380997156</v>
+        <v>325.9521091087573</v>
       </c>
     </row>
     <row r="7">
@@ -2022,28 +3605,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.89383399844195</v>
+        <v>64.27257280877528</v>
       </c>
       <c r="D7" t="n">
-        <v>7.507115420730777</v>
+        <v>3.114973175466682</v>
       </c>
       <c r="E7" t="n">
-        <v>47.58550177729312</v>
+        <v>61.31623721877904</v>
       </c>
       <c r="F7" t="n">
-        <v>50.23966788786753</v>
+        <v>61.40883581080773</v>
       </c>
       <c r="G7" t="n">
-        <v>52.89383399844195</v>
+        <v>64.3776715239254</v>
       </c>
       <c r="H7" t="n">
-        <v>55.54800010901637</v>
+        <v>67.11177328415573</v>
       </c>
       <c r="I7" t="n">
-        <v>58.20216621959079</v>
+        <v>67.12149214202077</v>
       </c>
     </row>
     <row r="8">
@@ -2053,28 +3636,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>46.5565857404249</v>
+        <v>59.80850083243372</v>
       </c>
       <c r="D8" t="n">
-        <v>13.25326323523937</v>
+        <v>2.548159863436597</v>
       </c>
       <c r="E8" t="n">
-        <v>37.18511343393678</v>
+        <v>56.977909507314</v>
       </c>
       <c r="F8" t="n">
-        <v>41.87084958718084</v>
+        <v>57.68535161496333</v>
       </c>
       <c r="G8" t="n">
-        <v>46.5565857404249</v>
+        <v>59.6915620731783</v>
       </c>
       <c r="H8" t="n">
-        <v>51.24232189366896</v>
+        <v>61.93856499084205</v>
       </c>
       <c r="I8" t="n">
-        <v>55.92805804691302</v>
+        <v>62.7857905819767</v>
       </c>
     </row>
     <row r="9">
@@ -2084,28 +3667,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.17283333333338</v>
+        <v>5.763372222222226</v>
       </c>
       <c r="D9" t="n">
-        <v>16.90989298665128</v>
+        <v>47.66513724206804</v>
       </c>
       <c r="E9" t="n">
-        <v>-28.12993333333334</v>
+        <v>-58.64028333333329</v>
       </c>
       <c r="F9" t="n">
-        <v>-22.15138333333336</v>
+        <v>-19.30939999999997</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.17283333333338</v>
+        <v>0.6679666666666719</v>
       </c>
       <c r="H9" t="n">
-        <v>-10.1942833333334</v>
+        <v>31.93543333333332</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.215733333333418</v>
+        <v>75.49518333333327</v>
       </c>
     </row>
     <row r="10">
@@ -2115,28 +3698,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.156594554250983</v>
+        <v>0.3360472770882647</v>
       </c>
       <c r="D10" t="n">
-        <v>0.108615766376424</v>
+        <v>0.09815242763710996</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07979160930243978</v>
+        <v>0.2085219150697526</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1181930817767114</v>
+        <v>0.2672223925424788</v>
       </c>
       <c r="G10" t="n">
-        <v>0.156594554250983</v>
+        <v>0.3379113502739699</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1949960267252546</v>
+        <v>0.3971055667207821</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2333974991995262</v>
+        <v>0.4714426680768611</v>
       </c>
     </row>
     <row r="11">
@@ -2146,28 +3729,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>6.337248258017052</v>
+        <v>4.464071976341557</v>
       </c>
       <c r="D11" t="n">
-        <v>5.746147814508596</v>
+        <v>3.99040747324052</v>
       </c>
       <c r="E11" t="n">
-        <v>2.274108172677764</v>
+        <v>-1.30787381785396</v>
       </c>
       <c r="F11" t="n">
-        <v>4.305678215347408</v>
+        <v>2.414014336732258</v>
       </c>
       <c r="G11" t="n">
-        <v>6.337248258017052</v>
+        <v>4.498649546614299</v>
       </c>
       <c r="H11" t="n">
-        <v>8.368818300686696</v>
+        <v>6.626264347407297</v>
       </c>
       <c r="I11" t="n">
-        <v>10.40038834335634</v>
+        <v>10.04040136823149</v>
       </c>
     </row>
     <row r="12">
@@ -2177,28 +3760,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.666666666666664</v>
+        <v>-19.78333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>9.663792676216152</v>
+        <v>29.13992297709641</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.5</v>
+        <v>-53.23333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.083333333333332</v>
+        <v>-40.86666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.666666666666664</v>
+        <v>-25.025</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.249999999999996</v>
+        <v>2.991666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>2.166666666666671</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="13">
@@ -2208,28 +3791,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3.112889868487696</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>44.68333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>44.68333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -2239,7 +3822,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -2270,28 +3853,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3.112889868487696</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>44.68333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>44.68333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>47.525</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -2301,28 +3884,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.09729274339634442</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.04937172370686935</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.05222273210106956</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.05222273210106956</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.09729274339634443</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
     </row>
     <row r="17">
@@ -2332,7 +3915,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -2363,28 +3946,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.09729274339634442</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.04937172370686935</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.05222273210106956</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.05222273210106956</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.09729274339634443</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
     </row>
     <row r="19">
@@ -2394,28 +3977,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>3.95</v>
+        <v>7.525000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.9219996384670298</v>
       </c>
       <c r="E19" t="n">
-        <v>3.95</v>
+        <v>6.683333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>3.95</v>
+        <v>6.683333333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95</v>
+        <v>7.525</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>8.366666666666667</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>8.366666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -2425,28 +4008,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>14.69166666666666</v>
+        <v>36.14444444444445</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01178511301977763</v>
+        <v>27.1920181643778</v>
       </c>
       <c r="E20" t="n">
-        <v>14.68333333333333</v>
+        <v>3.016666666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>14.6875</v>
+        <v>12.925</v>
       </c>
       <c r="G20" t="n">
-        <v>14.69166666666666</v>
+        <v>42.65</v>
       </c>
       <c r="H20" t="n">
-        <v>14.69583333333333</v>
+        <v>57.7375</v>
       </c>
       <c r="I20" t="n">
-        <v>14.7</v>
+        <v>62.76666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -2456,28 +4039,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>-10.74166666666667</v>
+        <v>-28.61944444444445</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01178511301977763</v>
+        <v>27.20764479305743</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.75</v>
+        <v>-56.08333333333334</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.74583333333333</v>
+        <v>-49.79166666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>-10.74166666666667</v>
+        <v>-35.125</v>
       </c>
       <c r="H21" t="n">
-        <v>-10.7375</v>
+        <v>-5.820833333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>-10.73333333333333</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="22">
@@ -2487,28 +4070,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1589453406816584</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.03497892599976014</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1270140960027041</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1270140960027041</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1589453406816584</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1908765853606127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1908765853606127</v>
       </c>
     </row>
     <row r="23">
@@ -2518,28 +4101,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2806013590182991</v>
+        <v>0.484321074758947</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1380103907203702</v>
+        <v>0.405916563201834</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1830132758657204</v>
+        <v>0.002166493188354733</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2318073174420097</v>
+        <v>0.1385295937763636</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2806013590182991</v>
+        <v>0.54761889554039</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3293954005945884</v>
+        <v>0.8142881005461697</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3781894421708778</v>
+        <v>0.9031778355480963</v>
       </c>
     </row>
     <row r="24">
@@ -2549,28 +4132,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.2156270830756994</v>
+        <v>-0.3253757340772886</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1380103907203702</v>
+        <v>0.407420889923044</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3132151662282782</v>
+        <v>-0.7761637395453922</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2644211246519888</v>
+        <v>-0.6393771375250341</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2156270830756994</v>
+        <v>-0.3886735548587316</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1668330414994101</v>
+        <v>0.004450124565817698</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1180389999231207</v>
+        <v>0.188710092172258</v>
       </c>
     </row>
     <row r="25">
@@ -2580,28 +4163,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>8.300000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="D25" t="n">
-        <v>11.38441917710342</v>
+        <v>3.067246322028931</v>
       </c>
       <c r="E25" t="n">
-        <v>0.25</v>
+        <v>11.75</v>
       </c>
       <c r="F25" t="n">
-        <v>4.275</v>
+        <v>11.75</v>
       </c>
       <c r="G25" t="n">
-        <v>8.300000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="H25" t="n">
-        <v>12.325</v>
+        <v>17.35</v>
       </c>
       <c r="I25" t="n">
-        <v>16.35</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="26">
@@ -2611,28 +4194,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>2.225</v>
+        <v>5.713888888888889</v>
       </c>
       <c r="D26" t="n">
-        <v>1.732411613907042</v>
+        <v>2.100037477619723</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6125</v>
+        <v>4.3375</v>
       </c>
       <c r="G26" t="n">
-        <v>2.225</v>
+        <v>4.45</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8375</v>
+        <v>7.025</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="27">
@@ -2642,28 +4225,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>6.075000000000001</v>
+        <v>8.836111111111112</v>
       </c>
       <c r="D27" t="n">
-        <v>9.652007563196374</v>
+        <v>3.867405341320468</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.75</v>
+        <v>2.85</v>
       </c>
       <c r="F27" t="n">
-        <v>2.662500000000001</v>
+        <v>7.3375</v>
       </c>
       <c r="G27" t="n">
-        <v>6.075000000000001</v>
+        <v>8.458333333333334</v>
       </c>
       <c r="H27" t="n">
-        <v>9.487500000000001</v>
+        <v>12.04166666666667</v>
       </c>
       <c r="I27" t="n">
-        <v>12.9</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="28">
@@ -2673,28 +4256,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>0.05141719462725855</v>
+        <v>0.07012436865027398</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07271489398104608</v>
+        <v>0.0422576278057351</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.03154860869050958</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02570859731362928</v>
+        <v>0.03154860869050958</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05141719462725855</v>
+        <v>0.07012436865027399</v>
       </c>
       <c r="H28" t="n">
-        <v>0.07712579194088783</v>
+        <v>0.1087001286100384</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1028343892545171</v>
+        <v>0.1087001286100384</v>
       </c>
     </row>
     <row r="29">
@@ -2704,28 +4287,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02818975672322354</v>
+        <v>0.06598134488738037</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01678158093663836</v>
+        <v>0.03178143803896245</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01632338704389566</v>
+        <v>0.04085835435001741</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0222565718835596</v>
+        <v>0.04326216992231931</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02818975672322354</v>
+        <v>0.050473616639225</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03412294156288748</v>
+        <v>0.0913588665623513</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04005612640255141</v>
+        <v>0.108236844142404</v>
       </c>
     </row>
     <row r="30">
@@ -2735,28 +4318,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02322743790403502</v>
+        <v>0.004143023762893619</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05593331304440772</v>
+        <v>0.05334705825718608</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.01632338704389566</v>
+        <v>-0.07668823545189443</v>
       </c>
       <c r="F30" t="n">
-        <v>0.003452025430069679</v>
+        <v>-0.01652119237641352</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02322743790403502</v>
+        <v>-0.002798450126431415</v>
       </c>
       <c r="H30" t="n">
-        <v>0.04300285037800036</v>
+        <v>0.0445980953297713</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06277826285196569</v>
+        <v>0.067841774260021</v>
       </c>
     </row>
     <row r="31">
@@ -2766,28 +4349,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>2.125</v>
+        <v>3.355555555555555</v>
       </c>
       <c r="D31" t="n">
-        <v>1.590990257669732</v>
+        <v>1.467941365263562</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2.016666666666667</v>
       </c>
       <c r="F31" t="n">
-        <v>1.5625</v>
+        <v>2.016666666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>2.125</v>
+        <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.6875</v>
+        <v>4.708333333333333</v>
       </c>
       <c r="I31" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="32">
@@ -2797,28 +4380,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>6.166666666666665</v>
+        <v>5.680555555555556</v>
       </c>
       <c r="D32" t="n">
-        <v>6.387531256718478</v>
+        <v>4.941102178739148</v>
       </c>
       <c r="E32" t="n">
-        <v>1.65</v>
+        <v>1.883333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>3.908333333333332</v>
+        <v>2.158333333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>6.166666666666665</v>
+        <v>3.141666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>8.424999999999997</v>
+        <v>9.837500000000002</v>
       </c>
       <c r="I32" t="n">
-        <v>10.68333333333333</v>
+        <v>12.01666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -2828,28 +4411,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>-4.041666666666665</v>
+        <v>-2.325000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>4.796540999048745</v>
+        <v>5.153895506205854</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.43333333333333</v>
+        <v>-10</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.737499999999997</v>
+        <v>-5.770833333333336</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.041666666666664</v>
+        <v>-0.5749999999999994</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.345833333333332</v>
+        <v>1.233333333333334</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6499999999999999</v>
+        <v>2.866666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -2859,28 +4442,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1802166157143374</v>
+        <v>0.279660536357128</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1441898613078723</v>
+        <v>0.1230922487823415</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07825898700519315</v>
+        <v>0.1675031909150123</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1292378013597653</v>
+        <v>0.1675031909150123</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1802166157143374</v>
+        <v>0.2727940994871458</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2311954300689096</v>
+        <v>0.3935344910167393</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2821742444234817</v>
+        <v>0.398684318669226</v>
       </c>
     </row>
     <row r="35">
@@ -2890,28 +4473,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4037174154949852</v>
+        <v>0.6497233593886754</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3017337192618181</v>
+        <v>0.2611797272780189</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1903594564923157</v>
+        <v>0.3612962495734293</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2970384359936505</v>
+        <v>0.430302590765105</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4037174154949852</v>
+        <v>0.6427375492395093</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5103963949963201</v>
+        <v>0.8708905805495375</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6170753744976548</v>
+        <v>0.9451362793530877</v>
       </c>
     </row>
     <row r="36">
@@ -2921,28 +4504,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2235007997806478</v>
+        <v>-0.3700628230315475</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1575438579539458</v>
+        <v>0.2894221647820405</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3349011300741731</v>
+        <v>-0.7776330884380754</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2792009649274105</v>
+        <v>-0.5300015438188649</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2235007997806478</v>
+        <v>-0.3699434497523635</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1678006346338852</v>
+        <v>-0.2101539455640259</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1121004694871225</v>
+        <v>0.03738806909579667</v>
       </c>
     </row>
     <row r="37">
@@ -2952,28 +4535,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>30.69923333333333</v>
+        <v>69.84166666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>13.43611307294223</v>
+        <v>6.079480515087894</v>
       </c>
       <c r="E37" t="n">
-        <v>21.19846666666666</v>
+        <v>64.3</v>
       </c>
       <c r="F37" t="n">
-        <v>25.94885</v>
+        <v>64.3</v>
       </c>
       <c r="G37" t="n">
-        <v>30.69923333333333</v>
+        <v>69.54166666666666</v>
       </c>
       <c r="H37" t="n">
-        <v>35.44961666666667</v>
+        <v>75.45833333333334</v>
       </c>
       <c r="I37" t="n">
-        <v>40.2</v>
+        <v>75.68333333333334</v>
       </c>
     </row>
     <row r="38">
@@ -2983,28 +4566,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>25.29966666666667</v>
+        <v>57.85550277777777</v>
       </c>
       <c r="D38" t="n">
-        <v>1.084701802340163</v>
+        <v>8.21335467162012</v>
       </c>
       <c r="E38" t="n">
-        <v>24.53266666666667</v>
+        <v>48.91343333333334</v>
       </c>
       <c r="F38" t="n">
-        <v>24.91616666666667</v>
+        <v>51.10416666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>25.29966666666667</v>
+        <v>57.16409166666666</v>
       </c>
       <c r="H38" t="n">
-        <v>25.68316666666667</v>
+        <v>64.87142916666666</v>
       </c>
       <c r="I38" t="n">
-        <v>26.06666666666667</v>
+        <v>67.36666666666666</v>
       </c>
     </row>
     <row r="39">
@@ -3014,28 +4597,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>5.399566666666662</v>
+        <v>11.9861638888889</v>
       </c>
       <c r="D39" t="n">
-        <v>12.35141127060207</v>
+        <v>10.30323464935172</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.33420000000001</v>
+        <v>-3.066666666666663</v>
       </c>
       <c r="F39" t="n">
-        <v>1.032683333333326</v>
+        <v>7.393816666666673</v>
       </c>
       <c r="G39" t="n">
-        <v>5.399566666666662</v>
+        <v>11.40591666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>9.766449999999997</v>
+        <v>17.55050416666668</v>
       </c>
       <c r="I39" t="n">
-        <v>14.13333333333333</v>
+        <v>26.51666666666668</v>
       </c>
     </row>
     <row r="40">
@@ -3045,28 +4628,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>25.87553851516734</v>
+        <v>63.60098342168468</v>
       </c>
       <c r="D40" t="n">
-        <v>12.25834148290547</v>
+        <v>3.990074267126172</v>
       </c>
       <c r="E40" t="n">
-        <v>17.20758212650452</v>
+        <v>59.94209820275543</v>
       </c>
       <c r="F40" t="n">
-        <v>21.54156032083593</v>
+        <v>59.95773080769569</v>
       </c>
       <c r="G40" t="n">
-        <v>25.87553851516734</v>
+        <v>63.50074917470226</v>
       </c>
       <c r="H40" t="n">
-        <v>30.20951670949874</v>
+        <v>67.27068498283633</v>
       </c>
       <c r="I40" t="n">
-        <v>34.54349490383015</v>
+        <v>67.35824904037362</v>
       </c>
     </row>
     <row r="41">
@@ -3076,28 +4659,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>19.154871283086</v>
+        <v>48.59904838315399</v>
       </c>
       <c r="D41" t="n">
-        <v>4.426431301214379</v>
+        <v>4.89177844938176</v>
       </c>
       <c r="E41" t="n">
-        <v>16.02491169354092</v>
+        <v>42.40876109368212</v>
       </c>
       <c r="F41" t="n">
-        <v>17.58989148831346</v>
+        <v>44.43810028340741</v>
       </c>
       <c r="G41" t="n">
-        <v>19.154871283086</v>
+        <v>50.40328255404857</v>
       </c>
       <c r="H41" t="n">
-        <v>20.71985107785854</v>
+        <v>52.32725361218235</v>
       </c>
       <c r="I41" t="n">
-        <v>22.28483087263108</v>
+        <v>52.96068060572409</v>
       </c>
     </row>
     <row r="42">
@@ -3107,28 +4690,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>6.720667232081336</v>
+        <v>15.00193503853068</v>
       </c>
       <c r="D42" t="n">
-        <v>7.831910181691089</v>
+        <v>6.312241984094287</v>
       </c>
       <c r="E42" t="n">
-        <v>1.182670432963601</v>
+        <v>6.985125291476798</v>
       </c>
       <c r="F42" t="n">
-        <v>3.951668832522468</v>
+        <v>10.8422991715204</v>
       </c>
       <c r="G42" t="n">
-        <v>6.720667232081336</v>
+        <v>15.44127977729231</v>
       </c>
       <c r="H42" t="n">
-        <v>9.489665631640204</v>
+        <v>17.34681103698453</v>
       </c>
       <c r="I42" t="n">
-        <v>12.25866403119907</v>
+        <v>24.85263162531097</v>
       </c>
     </row>
     <row r="43">
@@ -3138,28 +4721,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>22.692575</v>
+        <v>54.40071111111111</v>
       </c>
       <c r="D43" t="n">
-        <v>9.812249744926261</v>
+        <v>2.789230465492162</v>
       </c>
       <c r="E43" t="n">
-        <v>15.75426666666667</v>
+        <v>51.86666666666667</v>
       </c>
       <c r="F43" t="n">
-        <v>19.22342083333334</v>
+        <v>51.86666666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>22.692575</v>
+        <v>54.15213333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>26.16172916666666</v>
+        <v>56.9969</v>
       </c>
       <c r="I43" t="n">
-        <v>29.63088333333333</v>
+        <v>57.18333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -3169,28 +4752,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>44.23895555555555</v>
       </c>
       <c r="D44" t="n">
-        <v>3.653385036130489</v>
+        <v>6.923466913385276</v>
       </c>
       <c r="E44" t="n">
-        <v>17.41666666666667</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="F44" t="n">
-        <v>18.70833333333334</v>
+        <v>38.47916666666667</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>48.07499999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>21.29166666666666</v>
+        <v>48.82113333333332</v>
       </c>
       <c r="I44" t="n">
-        <v>22.58333333333333</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="45">
@@ -3200,28 +4783,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>2.692575</v>
+        <v>10.16175555555556</v>
       </c>
       <c r="D45" t="n">
-        <v>6.158864708795772</v>
+        <v>7.518517618155749</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.662400000000002</v>
+        <v>2.849600000000009</v>
       </c>
       <c r="F45" t="n">
-        <v>0.515087499999999</v>
+        <v>4.620833333333337</v>
       </c>
       <c r="G45" t="n">
-        <v>2.692575</v>
+        <v>8.052133333333337</v>
       </c>
       <c r="H45" t="n">
-        <v>4.8700625</v>
+        <v>14.53023333333333</v>
       </c>
       <c r="I45" t="n">
-        <v>7.047550000000001</v>
+        <v>21.84999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3231,28 +4814,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>19.56209111529103</v>
+        <v>53.01204165555043</v>
       </c>
       <c r="D46" t="n">
-        <v>9.792426364660521</v>
+        <v>0.8915553231207396</v>
       </c>
       <c r="E46" t="n">
-        <v>12.63780002856964</v>
+        <v>52.06628269419153</v>
       </c>
       <c r="F46" t="n">
-        <v>16.09994557193033</v>
+        <v>52.26554777520127</v>
       </c>
       <c r="G46" t="n">
-        <v>19.56209111529103</v>
+        <v>53.04846823496842</v>
       </c>
       <c r="H46" t="n">
-        <v>23.02423665865172</v>
+        <v>53.82311966809345</v>
       </c>
       <c r="I46" t="n">
-        <v>26.48638220201241</v>
+        <v>53.82311966809345</v>
       </c>
     </row>
     <row r="47">
@@ -3262,28 +4845,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>15.51246503986857</v>
+        <v>38.14200362985426</v>
       </c>
       <c r="D47" t="n">
-        <v>6.336207829199938</v>
+        <v>6.601695928799359</v>
       </c>
       <c r="E47" t="n">
-        <v>11.032089516834</v>
+        <v>30.72869553457691</v>
       </c>
       <c r="F47" t="n">
-        <v>13.27227727835129</v>
+        <v>32.5605110245949</v>
       </c>
       <c r="G47" t="n">
-        <v>15.51246503986857</v>
+        <v>38.20991544186779</v>
       </c>
       <c r="H47" t="n">
-        <v>17.75265280138586</v>
+        <v>43.61262048840102</v>
       </c>
       <c r="I47" t="n">
-        <v>19.99284056290314</v>
+        <v>45.61259697139702</v>
       </c>
     </row>
     <row r="48">
@@ -3293,28 +4876,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>4.049626075422455</v>
+        <v>14.87003802569616</v>
       </c>
       <c r="D48" t="n">
-        <v>3.456218535460583</v>
+        <v>6.662224832227899</v>
       </c>
       <c r="E48" t="n">
-        <v>1.605710511735639</v>
+        <v>6.650194461590203</v>
       </c>
       <c r="F48" t="n">
-        <v>2.827668293579047</v>
+        <v>9.848268909826398</v>
       </c>
       <c r="G48" t="n">
-        <v>4.049626075422455</v>
+        <v>14.7347857392747</v>
       </c>
       <c r="H48" t="n">
-        <v>5.271583857265863</v>
+        <v>20.02365252020156</v>
       </c>
       <c r="I48" t="n">
-        <v>6.493541639109271</v>
+        <v>23.09442413351654</v>
       </c>
     </row>
     <row r="49">
@@ -3324,28 +4907,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>57.68333333333334</v>
+        <v>176.7878138888889</v>
       </c>
       <c r="D49" t="n">
-        <v>47.82398863425016</v>
+        <v>4.654210831153225</v>
       </c>
       <c r="E49" t="n">
-        <v>23.86666666666667</v>
+        <v>172.54785</v>
       </c>
       <c r="F49" t="n">
-        <v>40.77500000000001</v>
+        <v>172.54785</v>
       </c>
       <c r="G49" t="n">
-        <v>57.68333333333334</v>
+        <v>176.5155916666666</v>
       </c>
       <c r="H49" t="n">
-        <v>74.59166666666667</v>
+        <v>181.0958333333333</v>
       </c>
       <c r="I49" t="n">
-        <v>91.5</v>
+        <v>181.3</v>
       </c>
     </row>
     <row r="50">
@@ -3355,28 +4938,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>73.239975</v>
+        <v>218.5890277777778</v>
       </c>
       <c r="D50" t="n">
-        <v>54.29162330416406</v>
+        <v>8.191279108422227</v>
       </c>
       <c r="E50" t="n">
-        <v>34.85</v>
+        <v>207.5</v>
       </c>
       <c r="F50" t="n">
-        <v>54.0449875</v>
+        <v>212.1053666666666</v>
       </c>
       <c r="G50" t="n">
-        <v>73.239975</v>
+        <v>222.4480083333333</v>
       </c>
       <c r="H50" t="n">
-        <v>92.4349625</v>
+        <v>224.1186375</v>
       </c>
       <c r="I50" t="n">
-        <v>111.62995</v>
+        <v>225.8048166666667</v>
       </c>
     </row>
     <row r="51">
@@ -3386,28 +4969,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>-15.55664166666666</v>
+        <v>-41.80121388888889</v>
       </c>
       <c r="D51" t="n">
-        <v>6.467634669913893</v>
+        <v>9.150414758641153</v>
       </c>
       <c r="E51" t="n">
-        <v>-20.12994999999999</v>
+        <v>-51.95214999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>-17.84329583333333</v>
+        <v>-48.15641666666669</v>
       </c>
       <c r="G51" t="n">
-        <v>-15.55664166666666</v>
+        <v>-43.4980166666667</v>
       </c>
       <c r="H51" t="n">
-        <v>-13.2699875</v>
+        <v>-36.83691666666667</v>
       </c>
       <c r="I51" t="n">
-        <v>-10.98333333333333</v>
+        <v>-27.53333333333327</v>
       </c>
     </row>
     <row r="52">
@@ -3417,28 +5000,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" t="n">
-        <v>58.72107956136848</v>
+        <v>208.5199931085477</v>
       </c>
       <c r="D52" t="n">
-        <v>56.02586334619869</v>
+        <v>2.995811618795742</v>
       </c>
       <c r="E52" t="n">
-        <v>19.10481166744055</v>
+        <v>205.5216138197976</v>
       </c>
       <c r="F52" t="n">
-        <v>38.91294561440451</v>
+        <v>205.907546772244</v>
       </c>
       <c r="G52" t="n">
-        <v>58.72107956136848</v>
+        <v>208.5926496243467</v>
       </c>
       <c r="H52" t="n">
-        <v>78.52921350833245</v>
+        <v>211.2493984460696</v>
       </c>
       <c r="I52" t="n">
-        <v>98.33734745529641</v>
+        <v>211.265551707941</v>
       </c>
     </row>
     <row r="53">
@@ -3448,28 +5031,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" t="n">
-        <v>68.91887786966899</v>
+        <v>237.4619161057367</v>
       </c>
       <c r="D53" t="n">
-        <v>67.24177614278476</v>
+        <v>11.36722788759843</v>
       </c>
       <c r="E53" t="n">
-        <v>21.37176198007807</v>
+        <v>228.0564978626206</v>
       </c>
       <c r="F53" t="n">
-        <v>45.14531992487353</v>
+        <v>229.2116932139315</v>
       </c>
       <c r="G53" t="n">
-        <v>68.91887786966899</v>
+        <v>232.3142072958215</v>
       </c>
       <c r="H53" t="n">
-        <v>92.69243581446445</v>
+        <v>246.7752422725921</v>
       </c>
       <c r="I53" t="n">
-        <v>116.4659937592599</v>
+        <v>252.313475062006</v>
       </c>
     </row>
     <row r="54">
@@ -3479,28 +5062,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C54" t="n">
-        <v>-10.19779830830051</v>
+        <v>-28.94192299718902</v>
       </c>
       <c r="D54" t="n">
-        <v>11.21591279658607</v>
+        <v>11.75805393179162</v>
       </c>
       <c r="E54" t="n">
-        <v>-18.12864630396349</v>
+        <v>-46.3626129147203</v>
       </c>
       <c r="F54" t="n">
-        <v>-14.163222306132</v>
+        <v>-36.94567503668691</v>
       </c>
       <c r="G54" t="n">
-        <v>-10.19779830830051</v>
+        <v>-24.62197022446091</v>
       </c>
       <c r="H54" t="n">
-        <v>-6.232374310469012</v>
+        <v>-21.29746431391479</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.266950312637519</v>
+        <v>-16.8021123016637</v>
       </c>
     </row>
   </sheetData>
@@ -3556,67 +5139,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>125.4501416666666</v>
+        <v>373.9857472222222</v>
       </c>
       <c r="D2" t="n">
-        <v>141.622975</v>
+        <v>368.222375</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.17283333333338</v>
+        <v>5.763372222222226</v>
       </c>
       <c r="F2" t="n">
-        <v>-16.17283333333338</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>16_clustered_phase_heatmap.png</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Constant phase dimensions omitted: charging_refueling_time_diff_min</t>
-        </is>
+        <v>0.6679666666666719</v>
       </c>
     </row>
   </sheetData>
